--- a/doc/Микросхемы/Общий список.xlsx
+++ b/doc/Микросхемы/Общий список.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Prog\GitHub\Sasha7b9\HomePC\doc\Микросхемы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B7AD39-E1C2-4BD0-9B90-04B01568752B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A115C4A1-1A6F-426E-A959-2F4255C4731A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
   <si>
     <t>155ЛН1</t>
   </si>
@@ -143,9 +143,6 @@
     <t>155ИД3</t>
   </si>
   <si>
-    <t>580ИК38</t>
-  </si>
-  <si>
     <t>556РТ5</t>
   </si>
   <si>
@@ -194,19 +191,25 @@
     <t>0/1</t>
   </si>
   <si>
-    <t>0/6</t>
-  </si>
-  <si>
     <t>0/3</t>
   </si>
   <si>
     <t>0/7</t>
   </si>
   <si>
-    <t>0/5</t>
-  </si>
-  <si>
     <t>0/8</t>
+  </si>
+  <si>
+    <t>1/3</t>
+  </si>
+  <si>
+    <t>580ВК38</t>
+  </si>
+  <si>
+    <t>1/6</t>
+  </si>
+  <si>
+    <t>3/5</t>
   </si>
 </sst>
 </file>
@@ -242,8 +245,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -572,7 +578,7 @@
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -582,7 +588,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -596,8 +602,8 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H6" t="s">
-        <v>52</v>
+      <c r="H6" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -615,7 +621,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -633,7 +639,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -651,7 +657,7 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -668,13 +674,13 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="H10" t="s">
-        <v>54</v>
+      <c r="H10" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -684,7 +690,7 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -702,12 +708,12 @@
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -717,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -747,7 +753,7 @@
         <v>4</v>
       </c>
       <c r="H15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -765,7 +771,7 @@
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -783,7 +789,7 @@
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -825,7 +831,7 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -842,7 +848,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -852,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -881,13 +887,13 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H24" t="s">
-        <v>57</v>
+      <c r="H24" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -897,7 +903,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -926,7 +932,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -936,12 +942,12 @@
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -951,7 +957,7 @@
         <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -968,8 +974,8 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H30" t="s">
-        <v>55</v>
+      <c r="H30" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -996,12 +1002,12 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35">
         <v>8</v>
@@ -1011,12 +1017,12 @@
         <v>8</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B37">
         <v>3</v>
@@ -1026,12 +1032,12 @@
         <v>3</v>
       </c>
       <c r="H37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -1041,12 +1047,12 @@
         <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40">
         <v>5</v>
@@ -1055,8 +1061,8 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H40" t="s">
-        <v>57</v>
+      <c r="H40" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -1085,7 +1091,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44">
         <v>8</v>
@@ -1095,7 +1101,7 @@
         <v>8</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -1112,7 +1118,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47">
         <v>3</v>
@@ -1122,7 +1128,7 @@
         <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -1140,7 +1146,7 @@
         <v>3</v>
       </c>
       <c r="H49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -1155,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -1170,12 +1176,12 @@
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -1185,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -1212,7 +1218,7 @@
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -1230,7 +1236,7 @@
         <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -1259,5 +1265,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/doc/Микросхемы/Общий список.xlsx
+++ b/doc/Микросхемы/Общий список.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Prog\GitHub\Sasha7b9\HomePC\doc\Микросхемы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A115C4A1-1A6F-426E-A959-2F4255C4731A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B92C72-D527-4B7E-877E-5C573FE33D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
   <si>
     <t>155ЛН1</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>3/5</t>
+  </si>
+  <si>
+    <t>155ИЕ7</t>
   </si>
 </sst>
 </file>
@@ -530,12 +533,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
     <col min="4" max="4" width="6.5703125" customWidth="1"/>
     <col min="5" max="5" width="6.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
@@ -563,16 +566,16 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2">
-        <f>SUM(B5:B58)</f>
+        <f>SUM(B5:B59)</f>
         <v>80</v>
       </c>
       <c r="E2">
-        <f>SUM(E5:E58)</f>
+        <f>SUM(E5:E59)</f>
         <v>162</v>
       </c>
       <c r="F2">
-        <f>SUM(F5:F58)</f>
-        <v>242</v>
+        <f>SUM(F5:F59)</f>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -584,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <f t="shared" ref="F5:F58" si="0">SUM($B5:$E5)</f>
+        <f t="shared" ref="F5:F59" si="0">SUM($B5:$E5)</f>
         <v>1</v>
       </c>
       <c r="H5" t="s">
@@ -613,12 +616,15 @@
       <c r="B7">
         <v>1</v>
       </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7" t="s">
         <v>52</v>
@@ -667,12 +673,15 @@
       <c r="B10">
         <v>6</v>
       </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>58</v>
@@ -680,47 +689,44 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H11" t="s">
-        <v>51</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H13" t="s">
         <v>50</v>
@@ -728,437 +734,470 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14">
-        <v>4</v>
+        <v>47</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15">
-        <v>3</v>
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="H15" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="H18" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="H21" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
       </c>
       <c r="F22">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H22" t="s">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23">
+        <v>41</v>
+      </c>
+      <c r="B23">
         <v>1</v>
       </c>
       <c r="F23">
         <f t="shared" si="0"/>
         <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>8</v>
       </c>
       <c r="F25">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H25" t="s">
-        <v>52</v>
+        <v>14</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26">
-        <v>7</v>
+        <v>46</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
       </c>
       <c r="F26">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F27">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
       </c>
       <c r="F28">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H28" t="s">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B30">
-        <v>3</v>
-      </c>
-      <c r="E30">
         <v>2</v>
       </c>
       <c r="F30">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>56</v>
+        <v>2</v>
+      </c>
+      <c r="H30" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>6</v>
       </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>38</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>8</v>
       </c>
-      <c r="F35">
+      <c r="F36">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H36" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>45</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>3</v>
       </c>
-      <c r="F37">
+      <c r="F38">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H38" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39">
-        <v>2</v>
-      </c>
-      <c r="F39">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H39" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>37</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>5</v>
       </c>
-      <c r="F40">
+      <c r="F41">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42">
-        <v>48</v>
-      </c>
-      <c r="F42">
-        <f t="shared" si="0"/>
-        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E43">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F43">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44">
+        <v>32</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>49</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>8</v>
       </c>
-      <c r="F44">
-        <f t="shared" si="0"/>
+      <c r="C45">
         <v>8</v>
       </c>
-      <c r="H44" t="s">
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="H45" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46">
-        <v>4</v>
-      </c>
-      <c r="F46">
-        <f t="shared" si="0"/>
-        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>44</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <v>3</v>
       </c>
-      <c r="F47">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="C48">
+        <v>6</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="H48" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>16</v>
-      </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="E49">
-        <v>2</v>
-      </c>
-      <c r="F49">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H49" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
       <c r="F50">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H50" t="s">
         <v>52</v>
@@ -1166,22 +1205,25 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
       <c r="F51">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -1196,71 +1238,92 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53">
+        <v>57</v>
+      </c>
+      <c r="B53">
         <v>1</v>
       </c>
       <c r="F53">
         <f t="shared" si="0"/>
         <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>35</v>
       </c>
-      <c r="B54">
-        <v>2</v>
-      </c>
-      <c r="F54">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H54" t="s">
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H55" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>4</v>
-      </c>
-      <c r="B56">
-        <v>2</v>
-      </c>
-      <c r="E56">
-        <v>10</v>
-      </c>
-      <c r="F56">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="H56" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F57">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58">
+        <v>5</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>8</v>
       </c>
-      <c r="E58">
-        <v>1</v>
-      </c>
-      <c r="F58">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/doc/Микросхемы/Общий список.xlsx
+++ b/doc/Микросхемы/Общий список.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Prog\GitHub\Sasha7b9\HomePC\doc\Микросхемы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B92C72-D527-4B7E-877E-5C573FE33D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D8DD6B-4A62-4093-9A90-5DC96E2728D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
   <si>
     <t>155ЛН1</t>
   </si>
@@ -213,6 +213,21 @@
   </si>
   <si>
     <t>155ИЕ7</t>
+  </si>
+  <si>
+    <t>580ИК57</t>
+  </si>
+  <si>
+    <t>580ВГ75</t>
+  </si>
+  <si>
+    <t>555ИД7</t>
+  </si>
+  <si>
+    <t>580ИК55</t>
+  </si>
+  <si>
+    <t>573РФ3</t>
   </si>
 </sst>
 </file>
@@ -533,13 +548,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="6.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
   </cols>
@@ -566,16 +581,24 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2">
-        <f>SUM(B5:B59)</f>
+        <f>SUM(B$5:B$64)</f>
         <v>80</v>
       </c>
+      <c r="C2">
+        <f>SUM(C$5:C$64)</f>
+        <v>48</v>
+      </c>
+      <c r="D2">
+        <f>SUM(D$5:D$64)</f>
+        <v>29</v>
+      </c>
       <c r="E2">
-        <f>SUM(E5:E59)</f>
+        <f>SUM(E5:E64)</f>
         <v>162</v>
       </c>
       <c r="F2">
-        <f>SUM(F5:F59)</f>
-        <v>285</v>
+        <f>SUM(F5:F64)</f>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -586,9 +609,15 @@
       <c r="B5">
         <v>1</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
       <c r="F5">
-        <f t="shared" ref="F5:F59" si="0">SUM($B5:$E5)</f>
-        <v>1</v>
+        <f t="shared" ref="F5:F64" si="0">SUM($B5:$E5)</f>
+        <v>3</v>
       </c>
       <c r="H5" t="s">
         <v>50</v>
@@ -655,12 +684,15 @@
       <c r="B9">
         <v>1</v>
       </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="s">
         <v>50</v>
@@ -694,6 +726,10 @@
       <c r="C11">
         <v>2</v>
       </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -721,12 +757,15 @@
       <c r="C13">
         <v>2</v>
       </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" t="s">
         <v>50</v>
@@ -739,9 +778,12 @@
       <c r="B14">
         <v>1</v>
       </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="s">
         <v>50</v>
@@ -787,12 +829,15 @@
       <c r="B17">
         <v>1</v>
       </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
       <c r="E17">
         <v>4</v>
       </c>
       <c r="F17">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" t="s">
         <v>52</v>
@@ -808,12 +853,15 @@
       <c r="C18">
         <v>3</v>
       </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
       <c r="E18">
         <v>8</v>
       </c>
       <c r="F18">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" t="s">
         <v>54</v>
@@ -904,12 +952,15 @@
       <c r="C24">
         <v>1</v>
       </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -922,12 +973,15 @@
       <c r="C25">
         <v>1</v>
       </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
       <c r="E25">
         <v>8</v>
       </c>
       <c r="F25">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>50</v>
@@ -940,9 +994,12 @@
       <c r="B26">
         <v>1</v>
       </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
       <c r="F26">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="s">
         <v>52</v>
@@ -1012,12 +1069,15 @@
       <c r="C31">
         <v>2</v>
       </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>56</v>
@@ -1072,203 +1132,201 @@
       <c r="B38">
         <v>3</v>
       </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
       <c r="F38">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H38" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40">
-        <v>2</v>
-      </c>
-      <c r="F40">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H40" t="s">
-        <v>50</v>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H41" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>37</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>5</v>
       </c>
-      <c r="F41">
+      <c r="F42">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H42" s="3" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43">
-        <v>48</v>
-      </c>
-      <c r="F43">
-        <f t="shared" si="0"/>
-        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E44">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F44">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45">
+        <v>8</v>
+      </c>
+      <c r="E45">
+        <v>32</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>49</v>
       </c>
-      <c r="B45">
+      <c r="B46">
         <v>8</v>
       </c>
-      <c r="C45">
+      <c r="C46">
         <v>8</v>
       </c>
-      <c r="F45">
+      <c r="F46">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H46" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47">
-        <v>4</v>
-      </c>
-      <c r="F47">
-        <f t="shared" si="0"/>
-        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>44</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>3</v>
       </c>
-      <c r="C48">
+      <c r="C49">
         <v>6</v>
       </c>
-      <c r="F48">
+      <c r="F49">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H49" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="E50">
-        <v>2</v>
-      </c>
-      <c r="F50">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="H50" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>32</v>
-      </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="F51">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H51" t="s">
-        <v>52</v>
+        <v>65</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
       <c r="F52">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H52" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53">
+        <v>62</v>
+      </c>
+      <c r="D53">
         <v>1</v>
       </c>
       <c r="F53">
         <f t="shared" si="0"/>
         <v>1</v>
-      </c>
-      <c r="H53" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54">
+        <v>32</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
         <v>1</v>
       </c>
       <c r="F54">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H54" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
       </c>
       <c r="F55">
         <f t="shared" si="0"/>
@@ -1278,52 +1336,127 @@
         <v>50</v>
       </c>
     </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>50</v>
+      </c>
+    </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="C57">
-        <v>2</v>
-      </c>
-      <c r="E57">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
       </c>
       <c r="F57">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="H57" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58">
-        <v>5</v>
+        <v>61</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
       </c>
       <c r="F58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H60" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="E62">
+        <v>10</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="H62" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63">
+        <v>5</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>8</v>
       </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="F59">
-        <f t="shared" si="0"/>
-        <v>2</v>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/doc/Микросхемы/Общий список.xlsx
+++ b/doc/Микросхемы/Общий список.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Prog\GitHub\Sasha7b9\HomePC\doc\Микросхемы\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My\HomePC\doc\Микросхемы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D8DD6B-4A62-4093-9A90-5DC96E2728D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9914448-F0FA-43B0-87C3-84963F6A306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,22 @@
     <definedName name="Миросхемы_есть_всего" comment="В наличии/всего требуеется">Лист1!$H$1</definedName>
     <definedName name="Название_компьютера">Лист1!$B$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1223,7 +1235,7 @@
         <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
